--- a/astro-site/public/dl/catering-checklist-templates/06-catering-event-checklists-by-type.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/06-catering-event-checklists-by-type.xlsx
@@ -629,9 +629,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>▸ Weddings, corporate events, cocktail receptions, formal banquets and outdoor events.</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>▸ Weddings, corporate events, cocktail receptions and outdoor events.</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Confirm the final guaranteed count with the wedding planner</t>
+          <t>Confirm with the wedding planner the guaranteed count already locked by 15 days out; any later change only as your contract allows</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1104,7 +1104,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G21">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1481,7 +1481,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G18">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Ceviche, tartare and any fish served raw or undercooked — parasite destruction: use only fish with documented freezing (−4 °F or below for 7 days, or −31 °F or below until solid + 15 h; FDA Food Code 3-402.11), keep the record 90 days and note the lot</t>
+          <t>Ceviche, tartare and any fish served raw or undercooked — parasite destruction: use only fish with documented freezing (−4 °F or below for 7 days, or −31 °F or below until solid + 15 h; FDA Food Code 3-402.11), keep the record 90 days and note the lot; put the raw/undercooked consumer advisory on the station sign or menu (FDA Food Code 3-603.11)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Every server must know the allergens on the tray they pass: an allergen card per tray, reviewed at the pre-event briefing. US: the 9 major allergens (FALCPA + FASTER Act: milk, egg, fish, shellfish, tree nuts, peanuts, wheat, soy and sesame); UK: 14</t>
+          <t>Every server must know the allergens on the tray they pass: an allergen card per tray, reviewed at the pre-event briefing. US: the 9 major allergens (FALCPA + FASTER Act: milk, egg, fish, crustacean shellfish, tree nuts, peanuts, wheat, soy and sesame); UK: 14</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1896,7 +1896,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G20">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Double the temperature checks: outdoors, food warms up much faster. Hold hot food at 135 °F or above and cold food at 41 °F or below. Food without temperature control falls under time as a public health control (FDA Food Code 3-501.19): 4 h max from when it comes out (mark the time), then serve or discard; cold food can go up to 6 h if it starts at 41 °F or below and never passes 70 °F. This needs a written procedure and, depending on your county, notice to the health department. In hot weather, refill more often and in smaller amounts</t>
+          <t>Double the temperature checks: outdoors, food warms up much faster. Hold hot food at 135 °F or above and cold food at 41 °F or below. Food without temperature control falls under time as a public health control (FDA Food Code 3-501.19): mark the time it came out of temperature control and serve it within 4 h; whatever is left at 4 h is discarded, and it can't go back into hot or cold holding to restart the clock. Cold food can go up to 6 h only if it came out at 41 °F or below and you check it never passes 70 °F: discard it as soon as it does, and at 6 h. This needs a written procedure and, depending on your county, notice to the health department. In hot weather, refill more often and in smaller amounts</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -2311,7 +2311,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G20">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/astro-site/public/dl/catering-checklist-templates/06-catering-event-checklists-by-type.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/06-catering-event-checklists-by-type.xlsx
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Ceviche, tartare and any fish served raw or undercooked — parasite destruction: use only fish with documented freezing (−4 °F or below for 7 days, or −31 °F or below until solid + 15 h; FDA Food Code 3-402.11), keep the record 90 days and note the lot; put the raw/undercooked consumer advisory on the station sign or menu (FDA Food Code 3-603.11)</t>
+          <t>Ceviche, tartare and any fish served raw or undercooked — parasite destruction: use only fish with documented freezing (−4 °F or below for 7 days; or −31 °F or below until solid, then 15 h at −31 °F or below or 24 h at −4 °F or below; FDA Food Code 3-402.11), keep the record 90 days (FDA Food Code 3-402.12) and note the lot; put the raw/undercooked consumer advisory on the station sign or menu (FDA Food Code 3-603.11)</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
